--- a/business_forms/043_eco_renovation_funding_application_form--business_forms.xlsx
+++ b/business_forms/043_eco_renovation_funding_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'label':_'government'}</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'label': 'Government'}</t>
+          <t>Government</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2001,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2001, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2002,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2002, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2003,_'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2003, 'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
